--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXX/LTAIPT_A63F30.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXX/LTAIPT_A63F30.xlsx
@@ -145,16 +145,16 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>5702C88A4690051F3B30566D3CF85766</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>603051B20C139E39B0A5410F9E1EF8A7</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
   </si>
   <si>
     <t>Aprobación y reprobación</t>
@@ -166,7 +166,7 @@
     <t>Reporte de índices de reprobación</t>
   </si>
   <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Servicios%20Educativos/</t>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Sub%20Servicios%20Escolares/</t>
   </si>
   <si>
     <t>XLS</t>
@@ -175,10 +175,10 @@
     <t>Departamento de Control Escolar</t>
   </si>
   <si>
-    <t>16/01/2023</t>
-  </si>
-  <si>
-    <t>En el periodo del 01 de julio al 30 de septiembre  de 2022 y en relación al ciclo escolar que abarca del  29 de agosto de 2022 al 27 de enero de 2023, se informa que debido a que la actividad académica del Colegio de Bachilleres del Estado de Tlaxcala, algunos de  los indicadores se generan por semestre, y la actualización se realiza de manera anual para cubrir el año lectivo autorizado por la Secretaría de Educación Pública.</t>
+    <t>24/04/2023</t>
+  </si>
+  <si>
+    <t>En relación al ciclo escolar que abarca en el periodo del 07 de febrero de 2023 al 21 d ejulio de 2023 se informa que debido a que la actividad académica del Colegio de Bachilleres del Estado de Tlaxcala, algunos de  los indicadores se generan por semestre, y la actualización se realiza de manera anual para cubrir el año lectivo autorizado por la Secretaría de Educación Pública.</t>
   </si>
 </sst>
 </file>
@@ -574,17 +574,16 @@
   <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.140625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="29.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="169.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="98.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="87.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="33.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="170.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="87.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="20" bestFit="1" customWidth="1"/>
